--- a/docentes/Hernandez Alonso Antonio Ascari - Estadisticos 20241.xlsx
+++ b/docentes/Hernandez Alonso Antonio Ascari - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -86,54 +86,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>RANGEL</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>DIEGO ANTONIO</t>
-  </si>
-  <si>
-    <t>DANA PAOLA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
   </si>
 </sst>
 </file>
@@ -755,16 +707,19 @@
         <v>28</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>28</v>
       </c>
-      <c r="E2">
-        <v>28</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -778,16 +733,19 @@
         <v>41</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>41</v>
       </c>
-      <c r="E3">
-        <v>41</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -801,16 +759,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>94.12</v>
+      </c>
+      <c r="H4">
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -824,16 +785,19 @@
         <v>40</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>40</v>
       </c>
-      <c r="E5">
-        <v>40</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>7.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -847,16 +811,19 @@
         <v>31</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>31</v>
       </c>
-      <c r="E6">
-        <v>31</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>7.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -870,16 +837,19 @@
         <v>36</v>
       </c>
       <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>36</v>
       </c>
-      <c r="E7">
-        <v>36</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
       <c r="G7">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H7">
+        <v>8.9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -893,16 +863,19 @@
         <v>23</v>
       </c>
       <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
         <v>23</v>
       </c>
-      <c r="E8">
-        <v>23</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
       <c r="G8">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H8">
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -958,16 +931,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>82.14</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -993,7 +966,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1019,7 +992,7 @@
         <v>94.12</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1036,16 +1009,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G5">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1062,16 +1035,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G6">
-        <v>83.87</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1097,7 +1070,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1123,7 +1096,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>
@@ -1133,7 +1106,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1163,144 +1136,6 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920013</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920359</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920237</v>
-      </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920071</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920053</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920242</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Hernandez Alonso Antonio Ascari - Estadisticos 20241.xlsx
+++ b/docentes/Hernandez Alonso Antonio Ascari - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="44">
   <si>
     <t>Mat</t>
   </si>
@@ -86,6 +86,69 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>VELASQUEZ</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
+    <t>EDUARDO EMER</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>ESTRELLA</t>
+  </si>
+  <si>
+    <t>MARIA ELISA</t>
+  </si>
+  <si>
+    <t>ULISES</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
   </si>
 </sst>
 </file>
@@ -483,10 +546,10 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -495,7 +558,7 @@
         <v>23</v>
       </c>
       <c r="G2">
-        <v>82.14</v>
+        <v>79.31</v>
       </c>
       <c r="H2">
         <v>7.8</v>
@@ -561,10 +624,10 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -573,7 +636,7 @@
         <v>35</v>
       </c>
       <c r="G5">
-        <v>87.5</v>
+        <v>79.55</v>
       </c>
       <c r="H5">
         <v>7.8</v>
@@ -639,10 +702,10 @@
         <v>16</v>
       </c>
       <c r="C8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -651,7 +714,7 @@
         <v>23</v>
       </c>
       <c r="G8">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="H8">
         <v>8.5</v>
@@ -704,10 +767,10 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -716,7 +779,7 @@
         <v>28</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>96.55</v>
       </c>
       <c r="H2">
         <v>7.8</v>
@@ -782,10 +845,10 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -794,7 +857,7 @@
         <v>40</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>90.91</v>
       </c>
       <c r="H5">
         <v>7.8</v>
@@ -860,10 +923,10 @@
         <v>16</v>
       </c>
       <c r="C8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -872,7 +935,7 @@
         <v>23</v>
       </c>
       <c r="G8">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="H8">
         <v>8.5</v>
@@ -925,10 +988,10 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -937,10 +1000,10 @@
         <v>28</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>96.55</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -966,7 +1029,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1003,22 +1066,22 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>86.36</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1044,7 +1107,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1081,10 +1144,10 @@
         <v>16</v>
       </c>
       <c r="C8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1093,10 +1156,10 @@
         <v>23</v>
       </c>
       <c r="G8">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="H8">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -1106,7 +1169,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1136,6 +1199,167 @@
         <v>22</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>22330051920150</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920058</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920067</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920335</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920076</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920053</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920242</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Hernandez Alonso Antonio Ascari - Estadisticos 20241.xlsx
+++ b/docentes/Hernandez Alonso Antonio Ascari - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="47">
   <si>
     <t>Mat</t>
   </si>
@@ -91,6 +91,9 @@
     <t>BAEZ</t>
   </si>
   <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -112,6 +115,9 @@
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
@@ -131,6 +137,9 @@
   </si>
   <si>
     <t>EDUARDO EMER</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
   </si>
   <si>
     <t>MONSERRAT</t>
@@ -1169,7 +1178,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1207,10 +1216,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1224,39 +1233,39 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920058</v>
+        <v>22330051920225</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920067</v>
+        <v>22330051920058</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1270,16 +1279,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920335</v>
+        <v>22330051920067</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1293,16 +1302,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920076</v>
+        <v>22330051920335</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1316,16 +1325,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920053</v>
+        <v>22330051920076</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1334,21 +1343,21 @@
         <v>13</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920242</v>
+        <v>21330051920053</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1357,6 +1366,29 @@
         <v>13</v>
       </c>
       <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920242</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Hernandez Alonso Antonio Ascari - Estadisticos 20241.xlsx
+++ b/docentes/Hernandez Alonso Antonio Ascari - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="35">
   <si>
     <t>Mat</t>
   </si>
@@ -91,70 +91,34 @@
     <t>BAEZ</t>
   </si>
   <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>VELASQUEZ</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>RANGEL</t>
   </si>
   <si>
     <t>EDUARDO EMER</t>
   </si>
   <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>ESTRELLA</t>
-  </si>
-  <si>
-    <t>MARIA ELISA</t>
-  </si>
-  <si>
-    <t>ULISES</t>
-  </si>
-  <si>
     <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
   </si>
   <si>
     <t>ROBERTO</t>
@@ -558,19 +522,19 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>79.31</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -636,19 +600,19 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>5</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G5">
-        <v>79.55</v>
+        <v>88.64</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -714,16 +678,16 @@
         <v>24</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G8">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="H8">
         <v>8.5</v>
@@ -779,19 +743,19 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>96.55</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -857,19 +821,19 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G5">
-        <v>90.91</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -935,16 +899,16 @@
         <v>24</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G8">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="H8">
         <v>8.5</v>
@@ -1000,19 +964,19 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>96.55</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1078,19 +1042,19 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G5">
-        <v>86.36</v>
+        <v>95.45</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1156,16 +1120,16 @@
         <v>24</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G8">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="H8">
         <v>8.9</v>
@@ -1178,7 +1142,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1216,10 +1180,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
         <v>31</v>
-      </c>
-      <c r="D2" t="s">
-        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1228,67 +1192,67 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920225</v>
+        <v>21330051920053</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
         <v>32</v>
       </c>
-      <c r="D3" t="s">
-        <v>40</v>
-      </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920058</v>
+        <v>21330051920112</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
         <v>33</v>
       </c>
-      <c r="D4" t="s">
-        <v>41</v>
-      </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920067</v>
+        <v>21330051920242</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
         <v>34</v>
-      </c>
-      <c r="D5" t="s">
-        <v>42</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1297,98 +1261,6 @@
         <v>13</v>
       </c>
       <c r="G5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920335</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920076</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920053</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920242</v>
-      </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9">
         <v>2</v>
       </c>
     </row>
